--- a/scripts/data/50m_Femenino_Absoluto_Estilos.xlsx
+++ b/scripts/data/50m_Femenino_Absoluto_Estilos.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -675,22 +675,22 @@
         <v>200 Estilos</v>
       </c>
       <c r="C7" t="str">
-        <v>ANA MORALES ORTOLA</v>
+        <v>APPOLINARIIA KOROLEVA</v>
       </c>
       <c r="D7">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="E7" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F7" t="str">
-        <v>00:02:48.29</v>
+        <v>00:02:47.78</v>
       </c>
       <c r="G7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H7" s="1">
-        <v>45095.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I7" t="str">
         <v>Deportista</v>
@@ -702,10 +702,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L7" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M7" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N7" t="str">
         <v>No</v>
@@ -719,22 +719,22 @@
         <v>200 Estilos</v>
       </c>
       <c r="C8" t="str">
-        <v>APPOLINARIIA KOROLEVA</v>
+        <v>ANA MORALES ORTOLA</v>
       </c>
       <c r="D8">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="E8" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F8" t="str">
-        <v>00:02:51.30</v>
+        <v>00:02:48.29</v>
       </c>
       <c r="G8">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="H8" s="1">
-        <v>46172.99949074074</v>
+        <v>45095.99949074074</v>
       </c>
       <c r="I8" t="str">
         <v>Deportista</v>
@@ -743,13 +743,13 @@
         <v>50m</v>
       </c>
       <c r="K8" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L8" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M8" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N8" t="str">
         <v>No</v>
@@ -1256,13 +1256,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F20" t="str">
-        <v>00:05:49.99</v>
+        <v>00:05:43.88</v>
       </c>
       <c r="G20">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="H20" s="1">
-        <v>46082.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I20" t="str">
         <v>Deportista</v>
@@ -1274,10 +1274,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L20" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M20" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N20" t="str">
         <v>No</v>
@@ -1335,22 +1335,22 @@
         <v>400 Estilos</v>
       </c>
       <c r="C22" t="str">
-        <v>MANUELA RADEANU</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D22">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E22" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F22" t="str">
-        <v>00:06:00.84</v>
+        <v>00:05:54.83</v>
       </c>
       <c r="G22">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="H22" s="1">
-        <v>44976.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I22" t="str">
         <v>Deportista</v>
@@ -1362,10 +1362,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L22" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M22" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N22" t="str">
         <v>No</v>
@@ -1379,22 +1379,22 @@
         <v>400 Estilos</v>
       </c>
       <c r="C23" t="str">
-        <v>SARA MESA BELTRAN</v>
+        <v>MANUELA RADEANU</v>
       </c>
       <c r="D23">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E23" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F23" t="str">
-        <v>00:06:17.34</v>
+        <v>00:06:00.84</v>
       </c>
       <c r="G23">
-        <v>344</v>
+        <v>393</v>
       </c>
       <c r="H23" s="1">
-        <v>45473.99949074074</v>
+        <v>44976.99949074074</v>
       </c>
       <c r="I23" t="str">
         <v>Deportista</v>
@@ -1406,10 +1406,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L23" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M23" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>Elche</v>
       </c>
       <c r="N23" t="str">
         <v>No</v>
@@ -1423,22 +1423,22 @@
         <v>400 Estilos</v>
       </c>
       <c r="C24" t="str">
-        <v>MARTA SERRANO MARCOS</v>
+        <v>SARA MESA BELTRAN</v>
       </c>
       <c r="D24">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E24" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F24" t="str">
-        <v>00:06:36.01</v>
+        <v>00:06:17.34</v>
       </c>
       <c r="G24">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="H24" s="1">
-        <v>46046.99949074074</v>
+        <v>45473.99949074074</v>
       </c>
       <c r="I24" t="str">
         <v>Deportista</v>
@@ -1450,10 +1450,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L24" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M24" t="str">
-        <v>Elche</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N24" t="str">
         <v>No</v>
@@ -1467,45 +1467,89 @@
         <v>400 Estilos</v>
       </c>
       <c r="C25" t="str">
+        <v>MARTA SERRANO MARCOS</v>
+      </c>
+      <c r="D25">
+        <v>2011</v>
+      </c>
+      <c r="E25" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F25" t="str">
+        <v>00:06:36.01</v>
+      </c>
+      <c r="G25">
+        <v>298</v>
+      </c>
+      <c r="H25" s="1">
+        <v>46046.99949074074</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J25" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L25" t="str">
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Elche</v>
+      </c>
+      <c r="N25" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26" t="str">
+        <v>400 Estilos</v>
+      </c>
+      <c r="C26" t="str">
         <v>MARTINA GOMEZ GONZALEZ</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>2007</v>
       </c>
-      <c r="E25" t="str">
-        <v>C.N. MEDITERRANEO VALENCIA</v>
-      </c>
-      <c r="F25" t="str">
+      <c r="E26" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F26" t="str">
         <v>00:06:36.44</v>
       </c>
-      <c r="G25">
+      <c r="G26">
         <v>297</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H26" s="1">
         <v>45255.99949074074</v>
       </c>
-      <c r="I25" t="str">
-        <v>Deportista</v>
-      </c>
-      <c r="J25" t="str">
-        <v>50m</v>
-      </c>
-      <c r="K25" t="str">
-        <v>Electrónico</v>
-      </c>
-      <c r="L25" t="str">
+      <c r="I26" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J26" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L26" t="str">
         <v>Trofeo Internacional Castalia Castellón - TICC23</v>
       </c>
-      <c r="M25" t="str">
+      <c r="M26" t="str">
         <v>Castellón</v>
       </c>
-      <c r="N25" t="str">
+      <c r="N26" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O26"/>
   </ignoredErrors>
 </worksheet>
 </file>